--- a/self_dataset/compare_results/tx.orijin.xlsx
+++ b/self_dataset/compare_results/tx.orijin.xlsx
@@ -420,13 +420,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>buggy_2_CareerOnToken.txt</t>
+          <t>buggy_11_ForTheBlockchain.txt</t>
         </is>
       </c>
     </row>
@@ -460,10 +460,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -471,208 +471,208 @@
         <v>105</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>buggy_11_Owned.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>115</v>
-      </c>
-      <c r="B7" t="n">
-        <v>25</v>
-      </c>
-      <c r="C7" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>buggy_3_CareerOnToken.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="D10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>buggy_14_ERC20.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>101</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>105</v>
+      </c>
+      <c r="B18" t="n">
         <v>5</v>
       </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>114</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>115</v>
-      </c>
-      <c r="B15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C15" t="n">
-        <v>24</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>buggy_4_PHO.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -680,209 +680,1427 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>115</v>
-      </c>
-      <c r="B22" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" t="n">
-        <v>19</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>buggy_14_SaveWon.txt</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>buggy_6_ChannelWallet.txt</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="A25" t="n">
+        <v>101</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B27" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D28" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>115</v>
-      </c>
-      <c r="B29" t="n">
-        <v>36</v>
-      </c>
-      <c r="C29" t="n">
-        <v>32</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-4</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>buggy_16_ExclusivePlatform.txt</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>buggy_7_AccountWallet.txt</t>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>SWC ID</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Before</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>After</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="A32" t="n">
+        <v>101</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B34" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>115</v>
+      </c>
+      <c r="B35" t="n">
+        <v>45</v>
+      </c>
+      <c r="C35" t="n">
+        <v>43</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>buggy_17_AZT.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>101</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>105</v>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>110</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>114</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115</v>
+      </c>
+      <c r="B43" t="n">
+        <v>34</v>
+      </c>
+      <c r="C43" t="n">
+        <v>32</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>buggy_18__Yesbuzz.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>101</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>105</v>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>114</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>115</v>
+      </c>
+      <c r="B50" t="n">
+        <v>41</v>
+      </c>
+      <c r="C50" t="n">
+        <v>35</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>buggy_18_Owned.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>101</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>105</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>114</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>115</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>buggy_19_ethBank.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>101</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>105</v>
+      </c>
+      <c r="B62" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>114</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>115</v>
+      </c>
+      <c r="B64" t="n">
+        <v>76</v>
+      </c>
+      <c r="C64" t="n">
+        <v>61</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>buggy_1_HotDollarsToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>101</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
+        <v>10</v>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>105</v>
+      </c>
+      <c r="B69" t="n">
+        <v>6</v>
+      </c>
+      <c r="C69" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>114</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>115</v>
+      </c>
+      <c r="B71" t="n">
+        <v>18</v>
+      </c>
+      <c r="C71" t="n">
+        <v>18</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>buggy_20_Stoppable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>101</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>105</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5</v>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>114</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>115</v>
+      </c>
+      <c r="B78" t="n">
+        <v>8</v>
+      </c>
+      <c r="C78" t="n">
         <v>7</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D78" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>buggy_2_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>101</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>105</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>110</v>
+      </c>
+      <c r="B84" t="n">
         <v>4</v>
       </c>
-      <c r="D35" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="C84" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>114</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
         <v>115</v>
       </c>
-      <c r="B36" t="n">
-        <v>34</v>
-      </c>
-      <c r="C36" t="n">
-        <v>31</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-3</v>
+      <c r="B86" t="n">
+        <v>18</v>
+      </c>
+      <c r="C86" t="n">
+        <v>25</v>
+      </c>
+      <c r="D86" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>buggy_3_CareerOnToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>101</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D90" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>105</v>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>110</v>
+      </c>
+      <c r="B92" t="n">
+        <v>4</v>
+      </c>
+      <c r="C92" t="n">
+        <v>5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>114</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>115</v>
+      </c>
+      <c r="B94" t="n">
+        <v>18</v>
+      </c>
+      <c r="C94" t="n">
+        <v>26</v>
+      </c>
+      <c r="D94" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>buggy_4_PHO.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>101</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="n">
+        <v>6</v>
+      </c>
+      <c r="D98" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>105</v>
+      </c>
+      <c r="B99" t="n">
+        <v>6</v>
+      </c>
+      <c r="C99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>114</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>115</v>
+      </c>
+      <c r="B101" t="n">
+        <v>19</v>
+      </c>
+      <c r="C101" t="n">
+        <v>19</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>buggy_5_Ownable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>3</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>115</v>
+      </c>
+      <c r="B107" t="n">
+        <v>5</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>buggy_6_ChannelWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>101</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>11</v>
+      </c>
+      <c r="D111" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>105</v>
+      </c>
+      <c r="B112" t="n">
+        <v>14</v>
+      </c>
+      <c r="C112" t="n">
+        <v>10</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>114</v>
+      </c>
+      <c r="B113" t="n">
+        <v>7</v>
+      </c>
+      <c r="C113" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>115</v>
+      </c>
+      <c r="B114" t="n">
+        <v>35</v>
+      </c>
+      <c r="C114" t="n">
+        <v>33</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>buggy_7_AccountWallet.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>101</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="n">
+        <v>13</v>
+      </c>
+      <c r="D118" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>105</v>
+      </c>
+      <c r="B119" t="n">
+        <v>13</v>
+      </c>
+      <c r="C119" t="n">
+        <v>12</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>114</v>
+      </c>
+      <c r="B120" t="n">
+        <v>7</v>
+      </c>
+      <c r="C120" t="n">
+        <v>7</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>115</v>
+      </c>
+      <c r="B121" t="n">
+        <v>35</v>
+      </c>
+      <c r="C121" t="n">
+        <v>33</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>buggy_8_Ownable.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>101</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>105</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>115</v>
+      </c>
+      <c r="B127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" t="n">
+        <v>5</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>buggy_9_XLToken.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>SWC ID</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>101</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" t="n">
+        <v>16</v>
+      </c>
+      <c r="D131" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>105</v>
+      </c>
+      <c r="B132" t="n">
+        <v>10</v>
+      </c>
+      <c r="C132" t="n">
+        <v>10</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>110</v>
+      </c>
+      <c r="B133" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>114</v>
+      </c>
+      <c r="B134" t="n">
+        <v>4</v>
+      </c>
+      <c r="C134" t="n">
+        <v>4</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>115</v>
+      </c>
+      <c r="B135" t="n">
+        <v>27</v>
+      </c>
+      <c r="C135" t="n">
+        <v>26</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="19">
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A123:D123"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A129:D129"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
